--- a/Thesis/node_states.xlsx
+++ b/Thesis/node_states.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://rockmtnins-my.sharepoint.com/personal/abigail_weeks_rmi_org/Documents/Documents/GitHub/Thesis/Thesis/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="819" documentId="8_{9E02A2B6-ECB6-4618-BD54-B9EF156C98D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3E5B7929-D3CF-407E-A9B1-2AEBC80CF18F}"/>
+  <xr:revisionPtr revIDLastSave="832" documentId="8_{9E02A2B6-ECB6-4618-BD54-B9EF156C98D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AECD370F-3498-4380-94E7-75D220268622}"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="29940" yWindow="1245" windowWidth="21600" windowHeight="11175" xr2:uid="{3ADA18EB-F48E-4EB7-BDCA-514FF055EF69}"/>
+    <workbookView xWindow="-14505" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{3ADA18EB-F48E-4EB7-BDCA-514FF055EF69}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1583,17 +1583,20 @@
         <v>189.78000000000003</v>
       </c>
       <c r="L2" s="22">
-        <v>100</v>
+        <f ca="1">120 + (250-120)*RAND()</f>
+        <v>243.23173226355055</v>
       </c>
       <c r="M2" s="22">
-        <v>500</v>
+        <f ca="1">250 + (500-250)*RAND()</f>
+        <v>277.12260627877782</v>
       </c>
       <c r="N2" s="22">
-        <v>800</v>
+        <f ca="1">500 + (800-500)*RAND()</f>
+        <v>601.49319383958868</v>
       </c>
       <c r="O2" s="22">
         <f ca="1">ROUND(RAND()*4, 2)</f>
-        <v>3.37</v>
+        <v>0.8</v>
       </c>
       <c r="P2" s="22">
         <v>27.54</v>
@@ -1801,17 +1804,20 @@
         <v>5543.1450000000004</v>
       </c>
       <c r="L3" s="22">
-        <v>100</v>
+        <f t="shared" ref="L3:L21" ca="1" si="4">120 + (250-120)*RAND()</f>
+        <v>190.71280628052389</v>
       </c>
       <c r="M3" s="22">
-        <v>500</v>
+        <f t="shared" ref="M3:M21" ca="1" si="5">250 + (500-250)*RAND()</f>
+        <v>426.23246843628385</v>
       </c>
       <c r="N3" s="22">
-        <v>800</v>
+        <f t="shared" ref="N3:N21" ca="1" si="6">500 + (800-500)*RAND()</f>
+        <v>788.17008239702113</v>
       </c>
       <c r="O3" s="22">
-        <f t="shared" ref="O3:O21" ca="1" si="4">ROUND(RAND()*4, 2)</f>
-        <v>0.73</v>
+        <f t="shared" ref="O3:O21" ca="1" si="7">ROUND(RAND()*4, 2)</f>
+        <v>2.5499999999999998</v>
       </c>
       <c r="P3" s="22">
         <v>31.18</v>
@@ -1829,19 +1835,19 @@
         <v>66170.899999999994</v>
       </c>
       <c r="U3" s="22">
-        <f t="shared" ref="U3:U21" si="5">T3/Q3</f>
+        <f t="shared" ref="U3:U21" si="8">T3/Q3</f>
         <v>1.790614353404069</v>
       </c>
       <c r="V3" s="27">
-        <f t="shared" ref="V3:V21" si="6">(AM3+AN3)/Q3</f>
+        <f t="shared" ref="V3:V21" si="9">(AM3+AN3)/Q3</f>
         <v>8.7970818010353322E-2</v>
       </c>
       <c r="W3" s="27">
-        <f t="shared" ref="W3:W21" si="7">(AT3+AU3)/Q3</f>
+        <f t="shared" ref="W3:W21" si="10">(AT3+AU3)/Q3</f>
         <v>9.4735930595356968E-2</v>
       </c>
       <c r="X3" s="22">
-        <f t="shared" ref="X3:X21" si="8">Q3*0.2</f>
+        <f t="shared" ref="X3:X21" si="11">Q3*0.2</f>
         <v>7390.8600000000006</v>
       </c>
       <c r="Y3" s="22" t="s">
@@ -2019,17 +2025,20 @@
         <v>1617.66</v>
       </c>
       <c r="L4" s="22">
-        <v>100</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>203.64501409193363</v>
       </c>
       <c r="M4" s="22">
-        <v>500</v>
+        <f t="shared" ca="1" si="5"/>
+        <v>398.12644855192855</v>
       </c>
       <c r="N4" s="22">
-        <v>800</v>
+        <f t="shared" ca="1" si="6"/>
+        <v>712.72365869840542</v>
       </c>
       <c r="O4" s="22">
-        <f t="shared" ca="1" si="4"/>
-        <v>1.3</v>
+        <f t="shared" ca="1" si="7"/>
+        <v>0.33</v>
       </c>
       <c r="P4" s="22">
         <v>32.33</v>
@@ -2047,19 +2056,19 @@
         <v>14664.8</v>
       </c>
       <c r="U4" s="22">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>1.3598160305626645</v>
       </c>
       <c r="V4" s="27">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>3.5328808278624682E-2</v>
       </c>
       <c r="W4" s="27">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>9.1344905604391527E-2</v>
       </c>
       <c r="X4" s="22">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>2156.88</v>
       </c>
       <c r="Y4" s="22" t="s">
@@ -2237,17 +2246,20 @@
         <v>1396.3500000000001</v>
       </c>
       <c r="L5" s="22">
-        <v>100</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>210.27107603822083</v>
       </c>
       <c r="M5" s="22">
-        <v>500</v>
+        <f t="shared" ca="1" si="5"/>
+        <v>479.13963266391323</v>
       </c>
       <c r="N5" s="22">
-        <v>800</v>
+        <f t="shared" ca="1" si="6"/>
+        <v>707.05189565259593</v>
       </c>
       <c r="O5" s="22">
-        <f t="shared" ca="1" si="4"/>
-        <v>3.74</v>
+        <f t="shared" ca="1" si="7"/>
+        <v>2.93</v>
       </c>
       <c r="P5" s="22">
         <v>31.47</v>
@@ -2265,19 +2277,19 @@
         <v>7515.7</v>
       </c>
       <c r="U5" s="22">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>0.80735847029756147</v>
       </c>
       <c r="V5" s="27">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>5.1885272317112471E-2</v>
       </c>
       <c r="W5" s="27">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="X5" s="22">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>1861.8000000000002</v>
       </c>
       <c r="Y5" s="22" t="s">
@@ -2455,17 +2467,20 @@
         <v>659.505</v>
       </c>
       <c r="L6" s="22">
-        <v>100</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>134.97099574911383</v>
       </c>
       <c r="M6" s="22">
-        <v>500</v>
+        <f t="shared" ca="1" si="5"/>
+        <v>434.14460666156481</v>
       </c>
       <c r="N6" s="22">
-        <v>800</v>
+        <f t="shared" ca="1" si="6"/>
+        <v>547.26314523577162</v>
       </c>
       <c r="O6" s="22">
-        <f t="shared" ca="1" si="4"/>
-        <v>1.71</v>
+        <f t="shared" ca="1" si="7"/>
+        <v>1.37</v>
       </c>
       <c r="P6" s="22">
         <v>40.11</v>
@@ -2483,19 +2498,19 @@
         <v>1349.9</v>
       </c>
       <c r="U6" s="22">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>0.30702572383833332</v>
       </c>
       <c r="V6" s="27">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>2.5018764073054796E-4</v>
       </c>
       <c r="W6" s="27">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="X6" s="22">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>879.34</v>
       </c>
       <c r="Y6" s="22" t="s">
@@ -2670,17 +2685,20 @@
         <v>4587.7950000000001</v>
       </c>
       <c r="L7" s="22">
-        <v>100</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>142.37607868142493</v>
       </c>
       <c r="M7" s="22">
-        <v>500</v>
+        <f t="shared" ca="1" si="5"/>
+        <v>441.28351950494607</v>
       </c>
       <c r="N7" s="22">
-        <v>800</v>
+        <f t="shared" ca="1" si="6"/>
+        <v>539.79738546601811</v>
       </c>
       <c r="O7" s="22">
-        <f t="shared" ca="1" si="4"/>
-        <v>3.63</v>
+        <f t="shared" ca="1" si="7"/>
+        <v>0.03</v>
       </c>
       <c r="P7" s="22">
         <v>25.55</v>
@@ -2698,19 +2716,19 @@
         <v>30386.9</v>
       </c>
       <c r="U7" s="22">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>0.99351322367281025</v>
       </c>
       <c r="V7" s="27">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>1.9290312666542424E-3</v>
       </c>
       <c r="W7" s="27">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>0.17579360019355703</v>
       </c>
       <c r="X7" s="22">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>6117.06</v>
       </c>
       <c r="Y7" s="22" t="s">
@@ -2888,17 +2906,20 @@
         <v>243.66000000000003</v>
       </c>
       <c r="L8" s="22">
-        <v>100</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>194.16450691970795</v>
       </c>
       <c r="M8" s="22">
-        <v>500</v>
+        <f t="shared" ca="1" si="5"/>
+        <v>313.99505449655078</v>
       </c>
       <c r="N8" s="22">
-        <v>800</v>
+        <f t="shared" ca="1" si="6"/>
+        <v>745.08349173234467</v>
       </c>
       <c r="O8" s="22">
-        <f t="shared" ca="1" si="4"/>
-        <v>0.43</v>
+        <f t="shared" ca="1" si="7"/>
+        <v>3.57</v>
       </c>
       <c r="P8" s="22">
         <v>32.69</v>
@@ -2916,19 +2937,19 @@
         <v>3569</v>
       </c>
       <c r="U8" s="22">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>2.1971189362226053</v>
       </c>
       <c r="V8" s="27">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>0.42655749815316418</v>
       </c>
       <c r="W8" s="27">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="X8" s="22">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>324.88000000000005</v>
       </c>
       <c r="Y8" s="22" t="s">
@@ -3106,17 +3127,20 @@
         <v>434.98500000000001</v>
       </c>
       <c r="L9" s="22">
-        <v>100</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>143.83214796460732</v>
       </c>
       <c r="M9" s="22">
-        <v>500</v>
+        <f t="shared" ca="1" si="5"/>
+        <v>348.82509922641503</v>
       </c>
       <c r="N9" s="22">
-        <v>800</v>
+        <f t="shared" ca="1" si="6"/>
+        <v>739.17789889067581</v>
       </c>
       <c r="O9" s="22">
-        <f t="shared" ca="1" si="4"/>
-        <v>2.91</v>
+        <f t="shared" ca="1" si="7"/>
+        <v>0.74</v>
       </c>
       <c r="P9" s="22">
         <v>31.28</v>
@@ -3134,19 +3158,19 @@
         <v>1289.2</v>
       </c>
       <c r="U9" s="22">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>0.44456705403634611</v>
       </c>
       <c r="V9" s="27">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>9.9968964447049891E-2</v>
       </c>
       <c r="W9" s="27">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="X9" s="22">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>579.98</v>
       </c>
       <c r="Y9" s="22" t="s">
@@ -3323,17 +3347,20 @@
         <v>4348.875</v>
       </c>
       <c r="L10" s="22">
-        <v>100</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>229.52568788766567</v>
       </c>
       <c r="M10" s="22">
-        <v>500</v>
+        <f t="shared" ca="1" si="5"/>
+        <v>461.80904241394614</v>
       </c>
       <c r="N10" s="22">
-        <v>800</v>
+        <f t="shared" ca="1" si="6"/>
+        <v>699.78663541718493</v>
       </c>
       <c r="O10" s="22">
-        <f t="shared" ca="1" si="4"/>
-        <v>2.72</v>
+        <f t="shared" ca="1" si="7"/>
+        <v>2.83</v>
       </c>
       <c r="P10" s="22">
         <v>37.020000000000003</v>
@@ -3351,19 +3378,19 @@
         <v>44067.6</v>
       </c>
       <c r="U10" s="22">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>1.5199655083211174</v>
       </c>
       <c r="V10" s="27">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>0.16648788479779253</v>
       </c>
       <c r="W10" s="27">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>2.6765542812796413E-2</v>
       </c>
       <c r="X10" s="22">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>5798.5</v>
       </c>
       <c r="Y10" s="22" t="s">
@@ -3544,17 +3571,20 @@
         <v>761.83500000000004</v>
       </c>
       <c r="L11" s="22">
-        <v>100</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>184.4304183330334</v>
       </c>
       <c r="M11" s="22">
-        <v>500</v>
+        <f t="shared" ca="1" si="5"/>
+        <v>374.97220107092295</v>
       </c>
       <c r="N11" s="22">
-        <v>800</v>
+        <f t="shared" ca="1" si="6"/>
+        <v>754.37908584543061</v>
       </c>
       <c r="O11" s="22">
-        <f t="shared" ca="1" si="4"/>
-        <v>1.59</v>
+        <f t="shared" ca="1" si="7"/>
+        <v>0.35</v>
       </c>
       <c r="P11" s="22">
         <v>31.36</v>
@@ -3572,19 +3602,19 @@
         <v>8885.9</v>
       </c>
       <c r="U11" s="22">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>1.7495717576640613</v>
       </c>
       <c r="V11" s="27">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>9.2716926893618698E-2</v>
       </c>
       <c r="W11" s="27">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="X11" s="22">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>1015.78</v>
       </c>
       <c r="Y11" s="22" t="s">
@@ -3769,17 +3799,20 @@
         <v>325.93500000000006</v>
       </c>
       <c r="L12" s="22">
-        <v>100</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>172.56183061725037</v>
       </c>
       <c r="M12" s="22">
-        <v>500</v>
+        <f t="shared" ca="1" si="5"/>
+        <v>339.48672568639665</v>
       </c>
       <c r="N12" s="22">
-        <v>800</v>
+        <f t="shared" ca="1" si="6"/>
+        <v>739.62520039055448</v>
       </c>
       <c r="O12" s="22">
-        <f t="shared" ca="1" si="4"/>
-        <v>3.09</v>
+        <f t="shared" ca="1" si="7"/>
+        <v>2.77</v>
       </c>
       <c r="P12" s="22">
         <v>30.97</v>
@@ -3797,19 +3830,19 @@
         <v>285.5</v>
       </c>
       <c r="U12" s="22">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>0.13139122831239358</v>
       </c>
       <c r="V12" s="27">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>2.4943623728657556E-2</v>
       </c>
       <c r="W12" s="27">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="X12" s="22">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>434.58000000000004</v>
       </c>
       <c r="Y12" s="22" t="s">
@@ -3984,17 +4017,20 @@
         <v>405.29999999999995</v>
       </c>
       <c r="L13" s="22">
-        <v>100</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>192.06357565337112</v>
       </c>
       <c r="M13" s="22">
-        <v>500</v>
+        <f t="shared" ca="1" si="5"/>
+        <v>412.19057904233586</v>
       </c>
       <c r="N13" s="22">
-        <v>800</v>
+        <f t="shared" ca="1" si="6"/>
+        <v>616.46915360780963</v>
       </c>
       <c r="O13" s="22">
-        <f t="shared" ca="1" si="4"/>
-        <v>1.74</v>
+        <f t="shared" ca="1" si="7"/>
+        <v>3.67</v>
       </c>
       <c r="P13" s="22">
         <v>30.64</v>
@@ -4012,19 +4048,19 @@
         <v>7954.7</v>
       </c>
       <c r="U13" s="22">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>2.9440044411546999</v>
       </c>
       <c r="V13" s="27">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>3.8860103626943004E-2</v>
       </c>
       <c r="W13" s="27">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="X13" s="22">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>540.4</v>
       </c>
       <c r="Y13" s="22" t="s">
@@ -4202,17 +4238,20 @@
         <v>499.51499999999999</v>
       </c>
       <c r="L14" s="22">
-        <v>100</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>195.00269200000514</v>
       </c>
       <c r="M14" s="22">
-        <v>500</v>
+        <f t="shared" ca="1" si="5"/>
+        <v>270.34483966920897</v>
       </c>
       <c r="N14" s="22">
-        <v>800</v>
+        <f t="shared" ca="1" si="6"/>
+        <v>585.97893217725118</v>
       </c>
       <c r="O14" s="22">
-        <f t="shared" ca="1" si="4"/>
-        <v>1.08</v>
+        <f t="shared" ca="1" si="7"/>
+        <v>1.68</v>
       </c>
       <c r="P14" s="22">
         <v>27.57</v>
@@ -4230,19 +4269,19 @@
         <v>14032.1</v>
       </c>
       <c r="U14" s="22">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>4.2137173057866129</v>
       </c>
       <c r="V14" s="27">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>0.1249512026665866</v>
       </c>
       <c r="W14" s="27">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="X14" s="22">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>666.02</v>
       </c>
       <c r="Y14" s="22" t="s">
@@ -4417,17 +4456,20 @@
         <v>547.56000000000006</v>
       </c>
       <c r="L15" s="22">
-        <v>100</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>223.29801376135299</v>
       </c>
       <c r="M15" s="22">
-        <v>500</v>
+        <f t="shared" ca="1" si="5"/>
+        <v>473.87133195361127</v>
       </c>
       <c r="N15" s="22">
-        <v>800</v>
+        <f t="shared" ca="1" si="6"/>
+        <v>666.02562380385575</v>
       </c>
       <c r="O15" s="22">
-        <f t="shared" ca="1" si="4"/>
-        <v>2.3199999999999998</v>
+        <f t="shared" ca="1" si="7"/>
+        <v>1.55</v>
       </c>
       <c r="P15" s="22">
         <v>28.71</v>
@@ -4445,19 +4487,19 @@
         <v>1130.9000000000001</v>
       </c>
       <c r="U15" s="22">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>0.30980166557089633</v>
       </c>
       <c r="V15" s="27">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>0.11779531010300241</v>
       </c>
       <c r="W15" s="27">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="X15" s="22">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>730.08</v>
       </c>
       <c r="Y15" s="22" t="s">
@@ -4632,17 +4674,20 @@
         <v>358.32000000000005</v>
       </c>
       <c r="L16" s="22">
-        <v>100</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>154.10526675845179</v>
       </c>
       <c r="M16" s="22">
-        <v>500</v>
+        <f t="shared" ca="1" si="5"/>
+        <v>428.06733936604496</v>
       </c>
       <c r="N16" s="22">
-        <v>800</v>
+        <f t="shared" ca="1" si="6"/>
+        <v>608.52548061031814</v>
       </c>
       <c r="O16" s="22">
-        <f t="shared" ca="1" si="4"/>
-        <v>2.0699999999999998</v>
+        <f t="shared" ca="1" si="7"/>
+        <v>2.67</v>
       </c>
       <c r="P16" s="22">
         <v>29.93</v>
@@ -4660,19 +4705,19 @@
         <v>398.5</v>
       </c>
       <c r="U16" s="22">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>0.16682016075016742</v>
       </c>
       <c r="V16" s="27">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="W16" s="27">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="X16" s="22">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>477.76000000000005</v>
       </c>
       <c r="Y16" s="22" t="s">
@@ -4847,17 +4892,20 @@
         <v>1797</v>
       </c>
       <c r="L17" s="22">
-        <v>100</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>198.24320393779971</v>
       </c>
       <c r="M17" s="22">
-        <v>500</v>
+        <f t="shared" ca="1" si="5"/>
+        <v>481.97618217356455</v>
       </c>
       <c r="N17" s="22">
-        <v>800</v>
+        <f t="shared" ca="1" si="6"/>
+        <v>772.33440902841096</v>
       </c>
       <c r="O17" s="22">
-        <f t="shared" ca="1" si="4"/>
-        <v>0.62</v>
+        <f t="shared" ca="1" si="7"/>
+        <v>0.99</v>
       </c>
       <c r="P17" s="22">
         <v>27.17</v>
@@ -4875,19 +4923,19 @@
         <v>126.8</v>
       </c>
       <c r="U17" s="22">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>1.0584307178631052E-2</v>
       </c>
       <c r="V17" s="27">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>2.5041736227045074E-4</v>
       </c>
       <c r="W17" s="27">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="X17" s="22">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>2396</v>
       </c>
       <c r="Y17" s="22" t="s">
@@ -5062,17 +5110,20 @@
         <v>1407.81</v>
       </c>
       <c r="L18" s="22">
-        <v>100</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>213.80647539191273</v>
       </c>
       <c r="M18" s="22">
-        <v>500</v>
+        <f t="shared" ca="1" si="5"/>
+        <v>330.14486379982657</v>
       </c>
       <c r="N18" s="22">
-        <v>800</v>
+        <f t="shared" ca="1" si="6"/>
+        <v>519.51973961953104</v>
       </c>
       <c r="O18" s="22">
-        <f t="shared" ca="1" si="4"/>
-        <v>0</v>
+        <f t="shared" ca="1" si="7"/>
+        <v>3.59</v>
       </c>
       <c r="P18" s="22">
         <v>32.1</v>
@@ -5090,19 +5141,19 @@
         <v>7073.9</v>
       </c>
       <c r="U18" s="22">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>0.75371321414111281</v>
       </c>
       <c r="V18" s="27">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>1.7953417009397576E-2</v>
       </c>
       <c r="W18" s="27">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>0.1319070044963454</v>
       </c>
       <c r="X18" s="22">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>1877.08</v>
       </c>
       <c r="Y18" s="22" t="s">
@@ -5280,17 +5331,20 @@
         <v>587.56500000000005</v>
       </c>
       <c r="L19" s="22">
-        <v>100</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>220.36848441133441</v>
       </c>
       <c r="M19" s="22">
-        <v>500</v>
+        <f t="shared" ca="1" si="5"/>
+        <v>297.3664060107954</v>
       </c>
       <c r="N19" s="22">
-        <v>800</v>
+        <f t="shared" ca="1" si="6"/>
+        <v>592.94640853011413</v>
       </c>
       <c r="O19" s="22">
-        <f t="shared" ca="1" si="4"/>
-        <v>1.45</v>
+        <f t="shared" ca="1" si="7"/>
+        <v>3.46</v>
       </c>
       <c r="P19" s="22">
         <v>38.18</v>
@@ -5308,19 +5362,19 @@
         <v>3155.7</v>
       </c>
       <c r="U19" s="22">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>0.80562150570575164</v>
       </c>
       <c r="V19" s="27">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>9.0883561818692407E-3</v>
       </c>
       <c r="W19" s="27">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="X19" s="22">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>783.42000000000007</v>
       </c>
       <c r="Y19" s="22" t="s">
@@ -5498,17 +5552,20 @@
         <v>2166.7200000000003</v>
       </c>
       <c r="L20" s="22">
-        <v>100</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>200.79845255629812</v>
       </c>
       <c r="M20" s="22">
-        <v>500</v>
+        <f t="shared" ca="1" si="5"/>
+        <v>252.72060098456794</v>
       </c>
       <c r="N20" s="22">
-        <v>800</v>
+        <f t="shared" ca="1" si="6"/>
+        <v>655.95508524857837</v>
       </c>
       <c r="O20" s="22">
-        <f t="shared" ca="1" si="4"/>
-        <v>0.16</v>
+        <f t="shared" ca="1" si="7"/>
+        <v>2.31</v>
       </c>
       <c r="P20" s="22">
         <v>26.82</v>
@@ -5526,19 +5583,19 @@
         <v>2238.1</v>
       </c>
       <c r="U20" s="22">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>0.15494157066902969</v>
       </c>
       <c r="V20" s="27">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>5.1921798848028359E-3</v>
       </c>
       <c r="W20" s="27">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>1.4988092600797519E-2</v>
       </c>
       <c r="X20" s="22">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>2888.96</v>
       </c>
       <c r="Y20" s="22" t="s">
@@ -5716,17 +5773,20 @@
         <v>1366.9949999999999</v>
       </c>
       <c r="L21" s="22">
-        <v>100</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>149.36509435571969</v>
       </c>
       <c r="M21" s="22">
-        <v>500</v>
+        <f t="shared" ca="1" si="5"/>
+        <v>264.19572151910245</v>
       </c>
       <c r="N21" s="22">
-        <v>800</v>
+        <f t="shared" ca="1" si="6"/>
+        <v>519.44784619869961</v>
       </c>
       <c r="O21" s="22">
-        <f t="shared" ca="1" si="4"/>
-        <v>1.31</v>
+        <f t="shared" ca="1" si="7"/>
+        <v>3.17</v>
       </c>
       <c r="P21" s="22">
         <v>27.83</v>
@@ -5744,19 +5804,19 @@
         <v>2587.1</v>
       </c>
       <c r="U21" s="22">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>0.28388179912874589</v>
       </c>
       <c r="V21" s="27">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>2.5270758122743684E-2</v>
       </c>
       <c r="W21" s="27">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="X21" s="22">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>1822.6599999999999</v>
       </c>
       <c r="Y21" s="22" t="s">
@@ -6744,20 +6804,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="T1:U1">
-    <cfRule type="colorScale" priority="94">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="X2:X21">
-    <cfRule type="colorScale" priority="4">
+  <conditionalFormatting sqref="P2:P21">
+    <cfRule type="colorScale" priority="3">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -6768,8 +6816,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P2:P21">
-    <cfRule type="colorScale" priority="3">
+  <conditionalFormatting sqref="R2:R21">
+    <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -6792,8 +6840,20 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R2:R21">
-    <cfRule type="colorScale" priority="1">
+  <conditionalFormatting sqref="T1:U1">
+    <cfRule type="colorScale" priority="94">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="X2:X21">
+    <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
